--- a/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
@@ -477,10 +477,10 @@
         <v>37</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>3</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>34</v>
@@ -489,7 +489,7 @@
         <v>91.89</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -503,16 +503,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -594,7 +597,7 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -617,7 +620,7 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -699,10 +702,10 @@
         <v>37</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>3</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>34</v>
@@ -711,7 +714,7 @@
         <v>91.89</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -725,16 +728,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
   </si>
 </sst>
 </file>
@@ -776,7 +785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -806,6 +815,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
   </si>
 </sst>
 </file>
@@ -512,19 +503,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -629,7 +620,7 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -737,19 +728,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -785,7 +776,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -815,29 +806,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920161</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
@@ -594,16 +594,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.89</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -617,16 +620,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.22</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -640,16 +646,19 @@
         <v>22</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>22</v>
       </c>
-      <c r="E4">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -714,7 +723,7 @@
         <v>91.89</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -731,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>97.22</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,7 +775,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20212.xlsx
@@ -594,7 +594,7 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -606,7 +606,7 @@
         <v>91.89</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -714,16 +714,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -749,7 +749,7 @@
         <v>97.22</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -775,7 +775,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
